--- a/sample_data/wedstrijd-data-2026-08-22.xlsx
+++ b/sample_data/wedstrijd-data-2026-08-22.xlsx
@@ -1078,10 +1078,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>209.28709</v>
+        <v>207.64688</v>
       </c>
       <c r="D2" t="n">
-        <v>227.114639</v>
+        <v>226.657179</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>288.569263</v>
+        <v>297.88765</v>
       </c>
       <c r="D6" t="n">
-        <v>284.164364</v>
+        <v>314.9036</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>308.488526</v>
+        <v>340.426985</v>
       </c>
       <c r="D13" t="n">
-        <v>229.084</v>
+        <v>211.926292</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>284.817931</v>
+        <v>318.23798</v>
       </c>
       <c r="D14" t="n">
-        <v>257.189171</v>
+        <v>305.020581</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>284.347479</v>
+        <v>285.396605</v>
       </c>
       <c r="D16" t="n">
-        <v>308.573956</v>
+        <v>317.50872</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>246.843982</v>
+        <v>229.504175</v>
       </c>
       <c r="D20" t="n">
-        <v>280.356979</v>
+        <v>300.112351</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>220.144933</v>
+        <v>205.164342</v>
       </c>
       <c r="D26" t="n">
-        <v>242.151988</v>
+        <v>241.138086</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>333.061734</v>
+        <v>348.195062</v>
       </c>
       <c r="D27" t="n">
-        <v>254.453992</v>
+        <v>256.736067</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>207.937943</v>
+        <v>205.228749</v>
       </c>
       <c r="D32" t="n">
-        <v>240.481713</v>
+        <v>240.265239</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>

--- a/sample_data/wedstrijd-data-2026-08-22.xlsx
+++ b/sample_data/wedstrijd-data-2026-08-22.xlsx
@@ -1078,10 +1078,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>207.64688</v>
+        <v>233.277711</v>
       </c>
       <c r="D2" t="n">
-        <v>226.657179</v>
+        <v>255.10592</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>422.717553</v>
+        <v>474.89557</v>
       </c>
       <c r="D3" t="n">
-        <v>248.543658</v>
+        <v>279.739467</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>182.217363</v>
+        <v>204.70931</v>
       </c>
       <c r="D4" t="n">
-        <v>163.083099</v>
+        <v>183.552377</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>364.598766</v>
+        <v>409.602907</v>
       </c>
       <c r="D5" t="n">
-        <v>266.172586</v>
+        <v>299.58108</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>297.88765</v>
+        <v>334.657325</v>
       </c>
       <c r="D6" t="n">
-        <v>314.9036</v>
+        <v>354.428537</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>449.810718</v>
+        <v>505.332971</v>
       </c>
       <c r="D7" t="n">
-        <v>164.878637</v>
+        <v>185.573281</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>406.459771</v>
+        <v>456.631012</v>
       </c>
       <c r="D8" t="n">
-        <v>267.20264</v>
+        <v>300.74042</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>206.65126</v>
+        <v>232.159197</v>
       </c>
       <c r="D9" t="n">
-        <v>296.333518</v>
+        <v>333.527642</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>399.500165</v>
+        <v>448.81235</v>
       </c>
       <c r="D10" t="n">
-        <v>139.622941</v>
+        <v>157.147631</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>255.553268</v>
+        <v>287.09741</v>
       </c>
       <c r="D11" t="n">
-        <v>318.865193</v>
+        <v>358.887367</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>371.479149</v>
+        <v>417.332568</v>
       </c>
       <c r="D12" t="n">
-        <v>273.147252</v>
+        <v>307.431167</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>340.426985</v>
+        <v>382.447489</v>
       </c>
       <c r="D13" t="n">
-        <v>211.926292</v>
+        <v>238.526094</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>318.23798</v>
+        <v>357.519591</v>
       </c>
       <c r="D14" t="n">
-        <v>305.020581</v>
+        <v>343.305057</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>371.231547</v>
+        <v>417.054403</v>
       </c>
       <c r="D15" t="n">
-        <v>130.410388</v>
+        <v>146.77877</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>285.396605</v>
+        <v>320.624451</v>
       </c>
       <c r="D16" t="n">
-        <v>317.50872</v>
+        <v>357.360637</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>397.228249</v>
+        <v>446.26</v>
       </c>
       <c r="D17" t="n">
-        <v>303.283309</v>
+        <v>341.349732</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>489.647743</v>
+        <v>550.087267</v>
       </c>
       <c r="D18" t="n">
-        <v>280.852158</v>
+        <v>316.103149</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>393.846982</v>
+        <v>442.461368</v>
       </c>
       <c r="D19" t="n">
-        <v>269.892058</v>
+        <v>303.767399</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>229.504175</v>
+        <v>257.832955</v>
       </c>
       <c r="D20" t="n">
-        <v>300.112351</v>
+        <v>337.780774</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>420.361504</v>
+        <v>472.248702</v>
       </c>
       <c r="D21" t="n">
-        <v>339.655465</v>
+        <v>382.287118</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>441.321149</v>
+        <v>495.795495</v>
       </c>
       <c r="D22" t="n">
-        <v>184.089571</v>
+        <v>207.195464</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>83.929817</v>
+        <v>94.289669</v>
       </c>
       <c r="D23" t="n">
-        <v>124.049836</v>
+        <v>139.619878</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>87.491291</v>
+        <v>98.290753</v>
       </c>
       <c r="D24" t="n">
-        <v>154.25669</v>
+        <v>173.618127</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>227.87693</v>
+        <v>256.004851</v>
       </c>
       <c r="D25" t="n">
-        <v>301.686041</v>
+        <v>339.551985</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>205.164342</v>
+        <v>230.488742</v>
       </c>
       <c r="D26" t="n">
-        <v>241.138086</v>
+        <v>271.404389</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>348.195062</v>
+        <v>391.174417</v>
       </c>
       <c r="D27" t="n">
-        <v>256.736067</v>
+        <v>288.960141</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>320.891013</v>
+        <v>360.500101</v>
       </c>
       <c r="D28" t="n">
-        <v>131.224781</v>
+        <v>147.695382</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>369.103508</v>
+        <v>414.66369</v>
       </c>
       <c r="D29" t="n">
-        <v>236.001703</v>
+        <v>265.623316</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>249.611276</v>
+        <v>280.42197</v>
       </c>
       <c r="D30" t="n">
-        <v>156.229955</v>
+        <v>175.839064</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>269.275794</v>
+        <v>302.513773</v>
       </c>
       <c r="D31" t="n">
-        <v>320.638254</v>
+        <v>360.882973</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>205.228749</v>
+        <v>230.561099</v>
       </c>
       <c r="D32" t="n">
-        <v>240.265239</v>
+        <v>270.421987</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>451.342525</v>
+        <v>507.053856</v>
       </c>
       <c r="D33" t="n">
-        <v>157.630358</v>
+        <v>177.415239</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
